--- a/training_history.xlsx
+++ b/training_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +509,64 @@
       </c>
       <c r="G3" t="n">
         <v>0.9133</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-05-16 12:46:51</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-05-16 12:47:27</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>0:00:35.895435</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>4200</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9214</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9322</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.7827</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-05-16 13:13:40</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-05-16 13:14:14</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0:00:34.710811</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>4199</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.9202</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.9449</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.7768</v>
       </c>
     </row>
   </sheetData>

--- a/training_history.xlsx
+++ b/training_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,6 +452,16 @@
           <t>R2</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Macro F1</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Weighted F1</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -481,6 +491,8 @@
       <c r="G2" t="n">
         <v>0.9133</v>
       </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -510,6 +522,8 @@
       <c r="G3" t="n">
         <v>0.9133</v>
       </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -539,6 +553,8 @@
       <c r="G4" t="n">
         <v>0.7827</v>
       </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -567,6 +583,132 @@
       </c>
       <c r="G5" t="n">
         <v>0.7768</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-20 16:19:17</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-05-20 16:19:55</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0:00:37.729667</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>4199</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.9202</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.9449</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.7768</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-05-20 16:24:35</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-05-20 16:25:10</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0:00:34.489773</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>4186</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.9296</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="n">
+        <v>0.9294</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.9295</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-05-20 16:27:08</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-05-20 16:27:41</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0:00:33.285222</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>4186</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.9296</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="n">
+        <v>0.9294</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.9294</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-05-20 20:45:58</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-05-20 20:46:32</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0:00:33.919578</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>4186</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.9356</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="n">
+        <v>0.9352</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.9353</v>
       </c>
     </row>
   </sheetData>

--- a/training_history.xlsx
+++ b/training_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -711,6 +711,130 @@
         <v>0.9353</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-05-21 12:29:21</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-05-21 12:29:56</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0:00:35.543209</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>4186</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.9415</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="n">
+        <v>0.9409</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.9409</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-05-21 12:34:57</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-05-21 12:35:36</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0:00:39.124829</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>4186</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.926</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="n">
+        <v>0.9255</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.9255</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-05-21 12:35:49</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-05-21 12:36:27</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0:00:38.258863</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>4186</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.9379</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="n">
+        <v>0.9379</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.9379999999999999</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-05-21 12:40:14</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-05-21 12:40:52</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0:00:37.875957</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>4186</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.9284</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="n">
+        <v>0.9283</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.9284</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/training_history.xlsx
+++ b/training_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -835,6 +835,37 @@
         <v>0.9284</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-05-21 12:43:40</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-05-21 12:44:27</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0:00:46.656252</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>4186</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.9379</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="n">
+        <v>0.9374</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.9374</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
